--- a/リリース管理表.xlsx
+++ b/リリース管理表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bdf0d5c0feacc685/Desktop/研修紹介HP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C9C2B2-C3E2-4E68-8E9A-3E5AB0C25F82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{35C33478-9150-4B0D-9C69-878E19613EAE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>コース名</t>
     <rPh sb="3" eb="4">
@@ -102,13 +102,35 @@
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C#で実践するビヘイビア駆動型開発</t>
+  </si>
+  <si>
+    <t>Javaで実践するビヘイビア駆動型開発</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハンズオンで学ぶGoプログラミング基礎</t>
+  </si>
+  <si>
+    <t>GoモダンWeb開発</t>
+  </si>
+  <si>
+    <t>オブジェクト指向要件定義</t>
+  </si>
+  <si>
+    <t>進化を続ける変化に強いソフトウェア設計</t>
+  </si>
+  <si>
+    <t>ソフトウェア品質管理</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,13 +145,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -168,10 +183,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="56" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE88B98-24D9-4A69-B40A-C3436C245FCB}">
-  <dimension ref="B1:E15"/>
+  <dimension ref="B1:E22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="44.296875" customWidth="1"/>
@@ -516,7 +531,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B1" s="2"/>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C2" s="1" t="s">
@@ -530,145 +545,222 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C5">
+      <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C6">
+      <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C7">
+      <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C8">
+      <c r="C8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C9">
+      <c r="C9" s="1">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="C10" s="1">
         <v>8</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="C11" s="1">
         <v>9</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="C12" s="1">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="C13" s="1">
         <v>11</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="C14" s="1">
         <v>12</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>46159</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="C15" s="1">
         <v>13</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="C16" s="1">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C18" s="1">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C19" s="1">
+        <v>17</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C20" s="1">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C21" s="1">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2">
         <v>46159</v>
       </c>
     </row>

--- a/リリース管理表.xlsx
+++ b/リリース管理表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bdf0d5c0feacc685/Desktop/研修紹介HP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9C9C2B2-C3E2-4E68-8E9A-3E5AB0C25F82}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F0D518D-85D5-4D36-9DC1-71622785C669}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{35C33478-9150-4B0D-9C69-878E19613EAE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>コース名</t>
     <rPh sb="3" eb="4">
@@ -124,6 +124,20 @@
   </si>
   <si>
     <t>ソフトウェア品質管理</t>
+  </si>
+  <si>
+    <t>C#テストコード基礎</t>
+    <rPh sb="8" eb="10">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C#基礎編</t>
+    <rPh sb="2" eb="5">
+      <t>キソヘン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -176,7 +190,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -184,9 +198,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -204,6 +215,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE88B98-24D9-4A69-B40A-C3436C245FCB}">
-  <dimension ref="B1:E22"/>
+  <dimension ref="B1:E25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="44.296875" customWidth="1"/>
@@ -548,7 +563,7 @@
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="2">
@@ -559,7 +574,7 @@
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="2">
@@ -570,7 +585,7 @@
       <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="2">
@@ -581,7 +596,7 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="2">
@@ -592,7 +607,7 @@
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="2">
@@ -603,7 +618,7 @@
       <c r="C8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="2">
@@ -614,7 +629,7 @@
       <c r="C9" s="1">
         <v>7</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2">
@@ -761,6 +776,39 @@
         <v>22</v>
       </c>
       <c r="E22" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C23" s="1">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C24" s="1">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C25" s="1">
+        <v>23</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2">
         <v>46159</v>
       </c>
     </row>

--- a/リリース管理表.xlsx
+++ b/リリース管理表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bdf0d5c0feacc685/Desktop/研修紹介HP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F0D518D-85D5-4D36-9DC1-71622785C669}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{E505DAA4-4E85-487B-82D9-8C31A2B90DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97D9B87-96A9-410F-B92A-13EFA2B0F00D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{35C33478-9150-4B0D-9C69-878E19613EAE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>コース名</t>
     <rPh sb="3" eb="4">
@@ -138,6 +138,9 @@
       <t>キソヘン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WSLで学ぶクラウド時代のLinux基礎</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE88B98-24D9-4A69-B40A-C3436C245FCB}">
-  <dimension ref="B1:E25"/>
+  <dimension ref="B1:E26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="44.296875" customWidth="1"/>
@@ -812,6 +815,17 @@
         <v>46159</v>
       </c>
     </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C26" s="1">
+        <v>24</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46159</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
